--- a/artfynd/A 60700-2019 artfynd.xlsx
+++ b/artfynd/A 60700-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123623858</v>
       </c>
       <c r="B2" t="n">
-        <v>74808</v>
+        <v>74814</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>123623879</v>
       </c>
       <c r="B3" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60700-2019 artfynd.xlsx
+++ b/artfynd/A 60700-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123623858</v>
+        <v>123623879</v>
       </c>
       <c r="B2" t="n">
-        <v>74814</v>
+        <v>95173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727377</v>
+        <v>727433</v>
       </c>
       <c r="R2" t="n">
-        <v>6369764</v>
+        <v>6369708</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123623879</v>
+        <v>123623858</v>
       </c>
       <c r="B3" t="n">
-        <v>95167</v>
+        <v>74817</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,27 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727433</v>
+        <v>727377</v>
       </c>
       <c r="R3" t="n">
-        <v>6369708</v>
+        <v>6369764</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 60700-2019 artfynd.xlsx
+++ b/artfynd/A 60700-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123623879</v>
+        <v>123623858</v>
       </c>
       <c r="B2" t="n">
-        <v>95173</v>
+        <v>74818</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727433</v>
+        <v>727377</v>
       </c>
       <c r="R2" t="n">
-        <v>6369708</v>
+        <v>6369764</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123623858</v>
+        <v>123623879</v>
       </c>
       <c r="B3" t="n">
-        <v>74817</v>
+        <v>95175</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727377</v>
+        <v>727433</v>
       </c>
       <c r="R3" t="n">
-        <v>6369764</v>
+        <v>6369708</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 60700-2019 artfynd.xlsx
+++ b/artfynd/A 60700-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123623858</v>
+        <v>123623879</v>
       </c>
       <c r="B2" t="n">
-        <v>74818</v>
+        <v>95683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727377</v>
+        <v>727433</v>
       </c>
       <c r="R2" t="n">
-        <v>6369764</v>
+        <v>6369708</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123623879</v>
+        <v>123623849</v>
       </c>
       <c r="B3" t="n">
-        <v>95175</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +798,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727433</v>
+        <v>727460</v>
       </c>
       <c r="R3" t="n">
-        <v>6369708</v>
+        <v>6369750</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,6 +893,116 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÅGP grupp kalkbarrskog </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123623858</v>
+      </c>
+      <c r="B4" t="n">
+        <v>74818</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Glose, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>727377</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6369764</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t xml:space="preserve">ÅGP grupp kalkbarrskog </t>
         </is>

--- a/artfynd/A 60700-2019 artfynd.xlsx
+++ b/artfynd/A 60700-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123623879</v>
+        <v>123623858</v>
       </c>
       <c r="B2" t="n">
-        <v>95683</v>
+        <v>74818</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727433</v>
+        <v>727377</v>
       </c>
       <c r="R2" t="n">
-        <v>6369708</v>
+        <v>6369764</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123623849</v>
+        <v>123623879</v>
       </c>
       <c r="B3" t="n">
-        <v>91010</v>
+        <v>95683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +797,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727460</v>
+        <v>727433</v>
       </c>
       <c r="R3" t="n">
-        <v>6369750</v>
+        <v>6369708</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123623858</v>
+        <v>123623849</v>
       </c>
       <c r="B4" t="n">
-        <v>74818</v>
+        <v>91010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,28 +908,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727377</v>
+        <v>727460</v>
       </c>
       <c r="R4" t="n">
-        <v>6369764</v>
+        <v>6369750</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 60700-2019 artfynd.xlsx
+++ b/artfynd/A 60700-2019 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123623879</v>
+        <v>123623849</v>
       </c>
       <c r="B3" t="n">
-        <v>95683</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +797,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727433</v>
+        <v>727460</v>
       </c>
       <c r="R3" t="n">
-        <v>6369708</v>
+        <v>6369750</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123623849</v>
+        <v>123623879</v>
       </c>
       <c r="B4" t="n">
-        <v>91010</v>
+        <v>95683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,34 +911,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727460</v>
+        <v>727433</v>
       </c>
       <c r="R4" t="n">
-        <v>6369750</v>
+        <v>6369708</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 60700-2019 artfynd.xlsx
+++ b/artfynd/A 60700-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123623858</v>
+        <v>123623849</v>
       </c>
       <c r="B2" t="n">
-        <v>74818</v>
+        <v>91010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727377</v>
+        <v>727460</v>
       </c>
       <c r="R2" t="n">
-        <v>6369764</v>
+        <v>6369750</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123623849</v>
+        <v>123623879</v>
       </c>
       <c r="B3" t="n">
-        <v>91010</v>
+        <v>95683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +801,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727460</v>
+        <v>727433</v>
       </c>
       <c r="R3" t="n">
-        <v>6369750</v>
+        <v>6369708</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123623879</v>
+        <v>123623858</v>
       </c>
       <c r="B4" t="n">
-        <v>95683</v>
+        <v>74818</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,27 +916,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727433</v>
+        <v>727377</v>
       </c>
       <c r="R4" t="n">
-        <v>6369708</v>
+        <v>6369764</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
